--- a/acc1_feed.xlsx
+++ b/acc1_feed.xlsx
@@ -34959,6 +34959,98 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a1_0925_YM_M21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79965236969</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Пресненская наб., 2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фонарь EDC с USB зажигалкой Yemao M21 на магните</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔦 Карманный фонарь Yemao M21 со встроенной USB-зажигалкой — маленький EDC фонарик и ветрозащитная спиральная зажигалка в одном корпусе весом 36 грамм.&lt;br&gt;&lt;br&gt;📌 Наличие уточняйте в чате — отвечаю быстро.&lt;br&gt;&lt;br&gt;Зажигалка без газа и бензина: спираль раскаляется от аккумулятора и поджигает на ветру и в мороз. Одного заряда хватает примерно на 50 поджигов. Второй конец — яркий фонарик до 300 люмен, а боковая RGB-панель светит красным и мигает красно-синим, если нужно обозначить себя на дороге. Магнит и клипса — крепится к металлу и карману.&lt;br&gt;&lt;br&gt;Что умеет:&lt;br&gt;▪️ Фонарь до 300 люмен, два режима и строб&lt;br&gt;▪️ RGB-подсветка сбоку, красно-синий сигнал&lt;br&gt;▪️ Спиральная USB-зажигалка, ~50 поджигов на заряд&lt;br&gt;▪️ До 390 минут работы&lt;br&gt;▪️ Магнит, стальная клипса&lt;br&gt;▪️ Зарядка Type-C, вес 36 г&lt;br&gt;&lt;br&gt;📦 Комплект: фонарь M21, кабель Type-C, упаковка.&lt;br&gt;&lt;br&gt;✅ Работаем в розницу и оптом — для опта напишите количество, посчитаю цену.&lt;br&gt;🛡 Гарантия 1 год. Товар новый, в упаковке.&lt;br&gt;🚚 Авито Доставка в любой город, отправляем в день заказа.&lt;br&gt;💸 Скидка 10% при заказе от 2 товаров — применится автоматически.&lt;br&gt;&lt;br&gt;По запросам: зажигалка с фонариком, usb зажигалка спиральная, edc фонарь маленький, фонарик аккумуляторный карманный, фонарь Yemao.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nRuH6B9.jpg | https://iili.io/nRuJqIp.jpg | https://iili.io/nRuJVvj.jpg | https://iili.io/nRuJgyv.jpg | https://iili.io/nRudHt2.jpg | https://iili.io/nRudwHG.jpg | https://iili.io/nRu2Fxp.jpg | https://iili.io/nRu2w11.jpg | https://iili.io/nRuIpZF.jpg | https://iili.io/nRuT7uS.jpg</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спорт и отдых</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1450</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Туризм и отдых на природе</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фонари и лампы</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/ahYgcxzxp_cBtQ</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnov1daniil@gmail.com</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РуГаджет РОЗНИЦА и ОПТ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="7">
     <dataValidation allowBlank="true" sqref="$B$5:$B$1048576" type="list">
@@ -37738,6 +37830,93 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a1_0925_YM_LY226</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79965236969</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Пресненская наб., 2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бинокль Comet 20х50 автофокус для охоты и рыбалки</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔭 Бинокль Comet AW-26 20х50 с автофокусом — мощный бинокль, который не нужно настраивать: поднёс к глазам и видишь резко.&lt;br&gt;&lt;br&gt;📌 Наличие уточняйте в чате — отвечаю быстро.&lt;br&gt;&lt;br&gt;Главная беда недорогих биноклей — ручная фокусировка: пока крутишь колёсико, цель уходит. Здесь фокус выставлен сразу, поэтому бинокль готов в ту же секунду — на охоте, на рыбалке, на стадионе. 20-кратное увеличение и объективы 50 мм дают светлую картинку и днём, и в сумерках.&lt;br&gt;&lt;br&gt;Что умеет:&lt;br&gt;▪️ Увеличение 20 крат&lt;br&gt;▪️ Диаметр объективов 50 мм&lt;br&gt;▪️ Автофокус — без ручной подстройки&lt;br&gt;▪️ Оптика с просветлением, меньше бликов&lt;br&gt;▪️ Настройка расстояния между окулярами&lt;br&gt;▪️ Прорезиненный корпус, защита от пыли и влаги&lt;br&gt;&lt;br&gt;📦 Комплект: бинокль, чехол, шейный ремень, салфетка для оптики.&lt;br&gt;&lt;br&gt;✅ Работаем в розницу и оптом — для опта напишите количество, посчитаю цену.&lt;br&gt;🛡 Гарантия 1 год. Товар новый, в упаковке.&lt;br&gt;🚚 Авито Доставка в любой город, отправляем в день заказа.&lt;br&gt;💸 Скидка 10% при заказе от 2 товаров — применится автоматически.&lt;br&gt;&lt;br&gt;По запросам: бинокль с автофокусом, бинокль 20х50, бинокль для охоты мощный, бинокль Comet, бинокль для рыбалки, бинокль туристический.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nRTm9jt.jpg | https://iili.io/nRTpzRp.jpg | https://iili.io/nRTyaQ1.jpg | https://iili.io/nRTygyl.jpg | https://iili.io/nRu9dn1.jpg | https://iili.io/nRu9Xcb.jpg | https://iili.io/nRu9voP.jpg | https://iili.io/nRu9SiF.jpg | https://iili.io/nRu9ZxI.jpg</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фототехника</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2990</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бинокли и телескопы</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnov1daniil@gmail.com</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/owrVauO9Csf_bQ</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РуГаджет РОЗНИЦА и ОПТ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="M5:M1048576">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -38305,6 +38484,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
         </is>
       </c>
     </row>
@@ -38949,6 +39133,11 @@
           <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="11">

--- a/acc1_feed.xlsx
+++ b/acc1_feed.xlsx
@@ -4586,7 +4586,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.9m5zWrawWodF7diKExndFUH6WIfD81KNxQ.FaP_RX-TDZ9xkPVE0_ugD25Gyaw-XDqYScYcKuRf_dE | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.PPsn8LawkBIRRxIfU_R5nRVQkhKXWZgYkQ.gmPF4yt6_AKgwHC_I58DFNgm_JS3DdYeOtEf-QUPu4A | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.pvRHZ7awCh1x0IgQB3W-kXXHCB33zgIX8Q.6mUVhXKqdDb80MWhJjDSCBkVXP7yYFV4kD5-6XPtNTY | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.ti-pELawGsafp5jLyQqsSpuwGMYZuRLMHw.vYBhif4szLH--ELA2-fJITalIpfvl2enV57uWjre6UU | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.UyruHbaw_8PYqn3OxGAEUdy9_cNetPfJWA.ae3qu2Susp-IO2RWNooh-gHpIvEd4mkDgQU_G9WQ1Pg | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.cflLQbaw3RB99l8dJXg5n3nh3xD76NUa_Q.QGdTJ9oUovjGLJSYaWYjLCQ3d364MiVYFM4wb2RwXo0 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.6sfpOLawRi7fj8QjsSfAvNuYRC5ZkU4kXw.NN_NAvE6XKqhoQeQ_Qoe_HBYTNb51UCo0vTF64ciOak | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.phPSZrawCvrk0Yj3kiCCaODGCPpizwLwZA.7QEHQdQn1oxDpkNC4gvywrVz74LSu2odBKPkCxiRlaM | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.FOihebawuAGXzjoMhS1Hk5PZugER0LALFw.t_Kj3KsfPeIg6NmlE-an2Uu4jeYX-YhkCX1fnY9T_eM | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.9uRyrrawWg1EGdgAEsX5gEAOWA3CB1IHxA.CQaAG-yLvCsPPTwB-ZgSbZdFodtCIENDl0FEOobMvbM</t>
+          <t xml:space="preserve">http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.pvRHZ7awCh1x0IgQB3W-kXXHCB33zgIX8Q.6mUVhXKqdDb80MWhJjDSCBkVXP7yYFV4kD5-6XPtNTY | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.9m5zWrawWodF7diKExndFUH6WIfD81KNxQ.FaP_RX-TDZ9xkPVE0_ugD25Gyaw-XDqYScYcKuRf_dE | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.PPsn8LawkBIRRxIfU_R5nRVQkhKXWZgYkQ.gmPF4yt6_AKgwHC_I58DFNgm_JS3DdYeOtEf-QUPu4A | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.ti-pELawGsafp5jLyQqsSpuwGMYZuRLMHw.vYBhif4szLH--ELA2-fJITalIpfvl2enV57uWjre6UU | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.UyruHbaw_8PYqn3OxGAEUdy9_cNetPfJWA.ae3qu2Susp-IO2RWNooh-gHpIvEd4mkDgQU_G9WQ1Pg | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.cflLQbaw3RB99l8dJXg5n3nh3xD76NUa_Q.QGdTJ9oUovjGLJSYaWYjLCQ3d364MiVYFM4wb2RwXo0 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.6sfpOLawRi7fj8QjsSfAvNuYRC5ZkU4kXw.NN_NAvE6XKqhoQeQ_Qoe_HBYTNb51UCo0vTF64ciOak | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.phPSZrawCvrk0Yj3kiCCaODGCPpizwLwZA.7QEHQdQn1oxDpkNC4gvywrVz74LSu2odBKPkCxiRlaM | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.FOihebawuAGXzjoMhS1Hk5PZugER0LALFw.t_Kj3KsfPeIg6NmlE-an2Uu4jeYX-YhkCX1fnY9T_eM | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.9uRyrrawWg1EGdgAEsX5gEAOWA3CB1IHxA.CQaAG-yLvCsPPTwB-ZgSbZdFodtCIENDl0FEOobMvbM</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4882,7 +4882,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8352310719</t>
+          <t xml:space="preserve">a1_0929_YM_T615</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4890,11 +4890,6 @@
           <t>Package</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>8352310719</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Даниил</t>
@@ -4912,17 +4907,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Налобный Фонарь с Управлением Взмахом Руки 2026</t>
+          <t xml:space="preserve">Налобный Фонарь с Датчиком Движения Yemao T615</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;НАЛОБНЫЙ ФОНАРЬ, КОТОРЫЙ ВКЛЮЧАЕТСЯ ВЗМАХОМ РУКИ 🙌&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;🔥 YEMAO T615 — компактный налобный фонарь с управлением жестом, яркостью до 500 Лм и поворотной головкой на 180°.&lt;/p&gt; &lt;p&gt;Представьте: руки в перчатках, в грязи, заняты инструментом или снастями — искать кнопку не нужно.&lt;/p&gt; &lt;p&gt;🙌 Провели рукой перед фонарём — &lt;strong&gt;включился.&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;Ещё один взмах — &lt;strong&gt;выключился.&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;Именно эта функция делает T615 совсем не похожим на обычные налобники.&lt;/p&gt; &lt;p&gt;🔥 ПОЧЕМУ T615 ЗАСЛУЖИВАЕТ ВНИМАНИЯ:&lt;/p&gt; &lt;p&gt;🙌 &lt;strong&gt;Управление жестом&lt;/strong&gt; — включение и выключение взмахом руки&lt;/p&gt; &lt;p&gt;💡 До 500 Лм — яркий свет для работы, прогулок и активного отдыха&lt;/p&gt; &lt;p&gt;🔦 Несколько вариантов освещения — направленный, рассеянный и красный свет&lt;/p&gt; &lt;p&gt;🔴 Красный свет — удобно ночью, когда важно сохранить адаптацию глаз к темноте&lt;/p&gt; &lt;p&gt;🔄 Поворот на 180° — направляйте свет именно туда, куда нужно&lt;/p&gt; &lt;p&gt;⚡ 7 режимов работы — под разные задачи&lt;/p&gt; &lt;p&gt;🔋 Встроенный аккумулятор 700 мА·ч&lt;/p&gt; &lt;p&gt;🔌 USB Type-C — удобно заряжать&lt;/p&gt; &lt;p&gt;🪶 Всего 48 грамм — лёгкий и компактный&lt;/p&gt; &lt;p&gt;💧 IPX4 — защита от брызг и дождя&lt;/p&gt; &lt;p&gt;🧲 Магнит + клипса — можно закрепить не только на голове&lt;/p&gt; &lt;p&gt;🎯 НЕ ТОЛЬКО НАЛОБНИК&lt;/p&gt; &lt;p&gt;T615 — универсальный фонарь для разных задач:&lt;/p&gt; &lt;p&gt;✔️ На голову — для рыбалки, походов и работы&lt;/p&gt; &lt;p&gt;✔️ На кепку — удобно для прогулок&lt;/p&gt; &lt;p&gt;✔️ На велосипед — крепление на руль&lt;/p&gt; &lt;p&gt;✔️ На одежду или сумку — благодаря клипсе&lt;/p&gt; &lt;p&gt;✔️ На металлическую поверхность — благодаря магниту&lt;/p&gt; &lt;p&gt;Поворотная конструкция позволяет быстро изменить направление света, не переставляя сам фонарь.&lt;/p&gt; &lt;p&gt;💥 ГДЕ ПРИГОДИТСЯ:&lt;/p&gt; &lt;p&gt;🎣 Рыбалка&lt;/p&gt; &lt;p&gt;🏕 Походы и кемпинг&lt;/p&gt; &lt;p&gt;🚲 Велосипед&lt;/p&gt; &lt;p&gt;🔧 Ремонт&lt;/p&gt; &lt;p&gt;🚗 Работа под капотом&lt;/p&gt; &lt;p&gt;🏠 Дом и гараж&lt;/p&gt; &lt;p&gt;🐕 Вечерние прогулки&lt;/p&gt; &lt;p&gt;⚡ На случай отключения электричества&lt;/p&gt; &lt;p&gt;Особенно удобно там, где обе руки постоянно заняты.&lt;/p&gt; &lt;p&gt;📦 В КОМПЛЕКТЕ:&lt;/p&gt; &lt;p&gt;• Фонарь YEMAO T615&lt;br&gt; • Налобное крепление&lt;br&gt; • Крепление на кепку&lt;br&gt; • Велокрепление&lt;br&gt; • Зарядный кабель Type-C&lt;/p&gt; &lt;p&gt;⭐ КОМПАКТНЫЙ, НО НЕ ОБЫЧНЫЙ&lt;/p&gt; &lt;p&gt;48 грамм • 500 Лм • 7 режимов • красный свет • магнит • клипса • USB-C&lt;/p&gt; &lt;p&gt;И главное — &lt;strong&gt;управление ВЗМАХОМ РУКИ 🙌&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;Один небольшой фонарь закрывает сразу несколько задач.&lt;/p&gt; &lt;p&gt;🏆 Гарантия 1 год&lt;/p&gt; &lt;p&gt;✅ Проверяю перед отправкой&lt;/p&gt; &lt;p&gt;📦 Товар в наличии&lt;/p&gt; &lt;p&gt;💸 При покупке от 2 штук — скидка 10%.&lt;/p&gt; &lt;p&gt;📩 Пишите — отвечу на вопросы и помогу подобрать подходящий вариант.&lt;/p&gt; &lt;p&gt;⭐ Добавьте объявление в избранное, чтобы не потерять.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;🙌 Налобный фонарь Yemao T615 с датчиком движения — включается взмахом руки&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Налобник, которому не нужна кнопка: провели ладонью перед фонарём — загорелся, ещё раз — погас. Удобно, когда руки в перчатках, в грязи или заняты снастями и инструментом. Подходит как налобный фонарь для рыбалки, бега, похода и работы в гараже.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Что умеет&lt;/strong&gt;&lt;br&gt;▪️ Датчик движения — включение и выключение жестом&lt;br&gt;▪️ До 500 люмен, луч до 150 метров&lt;br&gt;▪️ 7 режимов: яркий и средний луч, широкий боковой COB, луч + COB, красный свет и два режима SOS&lt;br&gt;▪️ Головка поворачивается на 180° — светит вперёд или под ноги&lt;br&gt;▪️ Вес 48 г — голова не устаёт&lt;br&gt;▪️ Влагозащита IPX4 — дождь и снег не страшны&lt;br&gt;▪️ Магнит на корпусе и клипса — крепится на кепку, одежду, капот&lt;br&gt;▪️ Зарядка Type-C, до 5 часов работы&lt;/p&gt;&lt;p&gt;&lt;strong&gt;3 в 1:&lt;/strong&gt; налобный, ручной и велосипедный — велокрепление на руль в комплекте.&lt;/p&gt;&lt;p&gt;📦 В комплекте: фонарь, эластичный ремешок, клипса, велокрепление, кабель Type-C. Цвет корпуса — синий или чёрный, кладём случайно.&lt;/p&gt;&lt;p&gt;🛡 Гарантия 1 год, проверяем перед отправкой.&lt;br&gt;🚚 Авито Доставка, отправка в день заказа.&lt;br&gt;💸 Скидка 10% при заказе от 2 товаров — применится автоматически.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.Qob6Y7aw7m_M1Gxi8i5F7urD7G9KyuZlTA.19QoUmAB9H94Nbg785_HPNphetQ7dkMhx0UqKp3plBw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.Yelc_rawzQBqSU8NEr9WhkxezwDsV8UK6g.GpZQm_o-kxj3uAV7n-3dJ21m6rEo0Vr2wE0rFNvlbhA | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.10LmjLawe6vQO_mmxIfwLPYseatWJXOhUA.5pL6pkLs9F9mA9NCBoyYM_lNZG99HDb6Mn7r8_VvTWw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.t0Ip1LawG6sfY5mmS-6tKjl0GauZfROhnw.VviMpSEt15jQ92S4MzClVQwur8SSr9yaqRuXtLr3C5s | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.aMV-VrawxCxI4UYhIg9Wqm72xizO_8wmyA.Vq8Hh9-ZSIMFDhSh7pkKJoH6CVIbLuu-fWWlhJxK7UA | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.sN_tVrawHDbb4Z47gTzctv32HjZd_xQ8Ww.7dF4-DnkDDPuZimmjCMHSmwlhFAowq54zXPaHU8q8Js | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.sqE6nrawHkgMKZxFUsSTzyo-HEiKNxZCjA.zW4iAekw2dHdjHGRSQ0ZLny4gnXmr9HYgDaYwOZpP7A | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.UdPc97aw_TrqQH838uJ1vcxX_zpsXvUwag.UCIvD7-Wf7BbYBvP2gLVjtUQRqVSw4LKehcrMsoQAxE | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.nj9n8rawMtZRRbDbV-DzVndSMNbXWzrc0Q.KEjnotfywAHLWSpbHMW32tBQWXnpurTrgDP6VzlT7E4</t>
+          <t xml:space="preserve">https://iili.io/nYj4FMG.jpg | https://iili.io/nYj40AP.jpg | https://iili.io/nYj4Sxn.jpg | https://iili.io/nYj4LRS.jpg | https://iili.io/nYj6dJV.jpg | https://iili.io/nYj6l1f.jpg | https://iili.io/nYj6Vm7.jpg | https://iili.io/nYj6O1j.jpg | https://iili.io/nYj6UmP.jpg | https://iili.io/nYj6sEJ.jpg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4968,16 +4963,6 @@
       <c r="R19" t="inlineStr">
         <is>
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Активно</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-10-19T15:43:42+03:00</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -5589,7 +5574,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;p&gt;🔥 &lt;strong&gt;НОВИНКА 2026 / ЯПОНИЯ / ГАРАНТИЯ 🔥&lt;br&gt; В КОМПЛЕКТЕ 1 Мощный Аккумулятор!!!!!!!! Не 2, как на видео!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;Профессиональный &lt;strong&gt;налобный фонарик YEMAO&lt;/strong&gt; с яркостью &lt;strong&gt;3000 люмен&lt;/strong&gt;. Видимость до 200 метров! То, что ты искал.&lt;/p&gt; &lt;p&gt;&lt;strong&gt;КЛЮЧЕВЫЕ ОСОБЕННОСТИ:&lt;/strong&gt;&lt;br&gt; 📌 Реальные 3000 люмен&lt;br&gt; 📌 Аккумулятор 21700 (5000 mAh) в комплекте 1 шт!&lt;br&gt; 📌 Зарядка Type-C&lt;br&gt; 📌 Авиационный алюминий&lt;br&gt; 📌 Влагозащита IPX4 (дождь/снег)&lt;/p&gt; &lt;p&gt;💰 &lt;strong&gt;ЦЕНА = КАЧЕСТВО.&lt;/strong&gt; Сборка уровня Fenix и Armytek, но стоит в 10 раз дешевле.&lt;/p&gt; &lt;p&gt;&lt;strong&gt;СМОТРИТЕ ВИДЕО В ОБЪЯВЛЕНИИ!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;&lt;strong&gt;ХАРАКТЕРИСТИКИ:&lt;/strong&gt;&lt;/p&gt; &lt;ul&gt; &lt;li&gt;Свет: 3000 люмен&lt;/li&gt; &lt;li&gt;Питание: Li-Ion 21700 (5000 мАч) /工作时间 до 1200 мин&lt;/li&gt; &lt;li&gt;Зарядка: USB-C (6ч)&lt;/li&gt; &lt;li&gt;Материал: алюминий&lt;/li&gt; &lt;li&gt;Режимы: 1 (Вкл/Выкл)&lt;/li&gt; &lt;/ul&gt; &lt;p&gt;&lt;strong&gt;КОМПЛЕКТ:&lt;/strong&gt;&lt;br&gt; ✅ Фонарь&lt;br&gt; ✅ Аккумулятор&lt;br&gt; ✅ Кабель Type-C&lt;br&gt; ✅ Крепление на голову&lt;/p&gt; &lt;p&gt;&lt;strong&gt;ПРИМЕНЕНИЕ:&lt;/strong&gt;&lt;br&gt; Для охоты, рыбалки, туризма, кемпинга, строительства, дачи, стройки, гаража, авто, мото, спасателям, охране, бойцам СВО.&lt;/p&gt; &lt;p&gt;&lt;strong&gt;УСЛОВИЯ:&lt;/strong&gt;&lt;br&gt; ✅ Официальная сертификация&lt;br&gt; ✅ Гарантия 1 год&lt;br&gt; ✅ Скидка 10% на второй товар&lt;br&gt; ✅ Отправка по РФ (Авито, СДЭК, Почта, Яндекс)&lt;/p&gt; &lt;p&gt;🎁 &lt;strong&gt;Подарок мужчине на 23 февраля или ДР!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;📞 &lt;strong&gt;ЗВОНИТЕ ИЛИ ПИШИТЕ СЕЙЧАС&lt;/strong&gt; — отправлю в день заказа!&lt;br&gt; 🏠 Самовывоз (если есть) / Встреча у метро.&lt;/p&gt; &lt;p&gt;❤️ &lt;strong&gt;Добавь в избранное&lt;/strong&gt;, чтобы не потерять выгодное предложение!&lt;/p&gt; &lt;p&gt;👇👇👇 &lt;strong&gt;СМОТРИТЕ ДРУГИЕ ТОВАРЫ В ПРОФИЛЕ&lt;/strong&gt; 👇👇👇&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;🔥 &lt;strong&gt;НОВИНКА 2026 / ЯПОНИЯ / ГАРАНТИЯ 🔥&lt;br&gt; В КОМПЛЕКТЕ 1 Мощный Аккумулятор!!!!!!!! Не 2, как на видео!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;Профессиональный &lt;strong&gt;налобный фонарик YEMAO&lt;/strong&gt; с яркостью &lt;strong&gt;3000 люмен&lt;/strong&gt;. Видимость до 200 метров! То, что ты искал.&lt;/p&gt; &lt;p&gt;&lt;strong&gt;КЛЮЧЕВЫЕ ОСОБЕННОСТИ:&lt;/strong&gt;&lt;br&gt; 📌 Реальные 3000 люмен&lt;br&gt; 📌 Аккумулятор 21700 (5000 mAh) в комплекте 1 шт!&lt;br&gt; 📌 Зарядка Type-C&lt;br&gt; 📌 Авиационный алюминий&lt;br&gt; 📌 Влагозащита IPX4 (дождь/снег)&lt;/p&gt; &lt;p&gt;💰 &lt;strong&gt;ЦЕНА = КАЧЕСТВО.&lt;/strong&gt; Сборка уровня Fenix и Armytek, но стоит в 10 раз дешевле.&lt;/p&gt; &lt;p&gt;&lt;strong&gt;СМОТРИТЕ ВИДЕО В ОБЪЯВЛЕНИИ!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;&lt;strong&gt;ХАРАКТЕРИСТИКИ:&lt;/strong&gt;&lt;/p&gt; &lt;ul&gt; &lt;li&gt;Свет: 3000 люмен&lt;/li&gt; &lt;li&gt;Питание: Li-Ion 21700 (5000 мАч) /время работы до 1200 мин&lt;/li&gt; &lt;li&gt;Зарядка: USB-C (6ч)&lt;/li&gt; &lt;li&gt;Материал: алюминий&lt;/li&gt; &lt;li&gt;Режимы: 1 (Вкл/Выкл)&lt;/li&gt; &lt;/ul&gt; &lt;p&gt;&lt;strong&gt;КОМПЛЕКТ:&lt;/strong&gt;&lt;br&gt; ✅ Фонарь&lt;br&gt; ✅ Аккумулятор&lt;br&gt; ✅ Кабель Type-C&lt;br&gt; ✅ Крепление на голову&lt;/p&gt; &lt;p&gt;&lt;strong&gt;ПРИМЕНЕНИЕ:&lt;/strong&gt;&lt;br&gt; Для охоты, рыбалки, туризма, кемпинга, строительства, дачи, стройки, гаража, авто, мото, спасателям, охране, бойцам СВО.&lt;/p&gt; &lt;p&gt;&lt;strong&gt;УСЛОВИЯ:&lt;/strong&gt;&lt;br&gt; ✅ Официальная сертификация&lt;br&gt; ✅ Гарантия 1 год&lt;br&gt; ✅ Скидка 10% на второй товар&lt;br&gt; ✅ Отправка по РФ (Авито, СДЭК, Почта, Яндекс)&lt;/p&gt; &lt;p&gt;🎁 &lt;strong&gt;Подарок мужчине на 23 февраля или ДР!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;📞 &lt;strong&gt;ЗВОНИТЕ ИЛИ ПИШИТЕ СЕЙЧАС&lt;/strong&gt; — отправлю в день заказа!&lt;br&gt; 🏠 Самовывоз (если есть) / Встреча у метро.&lt;/p&gt; &lt;p&gt;❤️ &lt;strong&gt;Добавь в избранное&lt;/strong&gt;, чтобы не потерять выгодное предложение!&lt;/p&gt; &lt;p&gt;👇👇👇 &lt;strong&gt;СМОТРИТЕ ДРУГИЕ ТОВАРЫ В ПРОФИЛЕ&lt;/strong&gt; 👇👇👇&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -8553,7 +8538,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7610911108</t>
+          <t xml:space="preserve">a1_0929_SvetiKuri</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8561,11 +8546,6 @@
           <t>Package</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7610911108</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Даниил</t>
@@ -8583,17 +8563,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Адово Мощный Фонарь с Прикуривателем "Сатана"</t>
+          <t xml:space="preserve">Фонарь с Прикуривателем Адово Мощный «Сатана»</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;🔥HACТОЯЩAЯ ГАPАНТИЯ 1 ГОД! 2 очень мощных АКБ в комплекте!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;Бeзупрeчный рейтинг ⭐️⭐️⭐️⭐️⭐️&lt;/p&gt; &lt;p&gt;Забудь про ситуации, когда темно и нечем поджечь! Этот светодиодный ручной фонарь решает всё сразу: светит как прожектор и в тот же момент включает встроенный прикуриватель.&lt;/p&gt; &lt;p&gt;❗️&lt;strong&gt;Смотри видео до конца!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;&lt;strong&gt;Почему Фонарик Сатаны?&lt;/strong&gt;&lt;/p&gt; &lt;ul&gt; &lt;li&gt;Свет такой мощный, что легко пробивает тьму на десятки метров. Дорога, палатка или машина — будет как днём.&lt;/li&gt; &lt;li&gt;Встроенный прикуриватель работает без газа и спичек. Разожжёт костёр, свечу, горелку и даже сигарету — на морозе и при ветре. Жжет как Сатана!&lt;/li&gt; &lt;li&gt;Прочный корпус с ударным торцом и складным ножом — можно выбить стекло или использовать как резак в экстренной ситуации.&lt;/li&gt; &lt;/ul&gt; &lt;p&gt;⚠️ Свет реально мощный, лучше не направлять в глаза.&lt;/p&gt; &lt;p&gt;&lt;strong&gt;Где пригодится:&lt;/strong&gt;&lt;/p&gt; &lt;ul&gt; &lt;li&gt;На трассе ночью — и дорогу подсветит, и сигнальный огонь разведёшь.&lt;/li&gt; &lt;li&gt;В походе — освещает лагерь и заменяет зажигалку.&lt;/li&gt; &lt;li&gt;На рыбалке или охоте — спасёт, когда темно и нужен огонь.&lt;/li&gt; &lt;li&gt;Дома — всегда под рукой, если отключили свет.&lt;/li&gt; &lt;/ul&gt; &lt;p&gt;А ещё он выглядит брутально и стильно — идеально в рюкзак, бардачок или как часть EDC-набора.&lt;/p&gt; &lt;p&gt;&lt;strong&gt;Фишки:&lt;/strong&gt;&lt;br&gt; 🔋 Индикатор заряда в %&lt;br&gt; 📱 Power Bank для телефона&lt;br&gt; 💡 4 режима фонаря: 100%, 50%, стробоскоп, SOS&lt;br&gt; ⛺ 4 режима кемпинг-света (до 48 ч работы)&lt;br&gt; 🦾 Авиационный алюминий, морозы до –30°C&lt;/p&gt; &lt;p&gt;🎁 Идеальный подарок для мужчин, автолюбителей, туристов и просто любителей крутых вещей.&lt;/p&gt; &lt;p&gt;🚚 Отправка в день заказа по всей России.&lt;/p&gt; &lt;p&gt;👉 Жми «Купить с доставкой» — пусть тьма сама боится твоей яркости!&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;🔥 Фонарь с прикуривателем «Сатана» — мощный аккумуляторный фонарь и турбозажигалка в одном корпусе&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ручной светодиодный фонарь, который ещё и поджигает: встроенный прикуриватель работает без газа и спичек, на ветру и в мороз. Его берут как фонарь с зажигалкой в машину, тактический фонарик в поход и на рыбалку.&lt;/p&gt;&lt;p&gt;🔋 В комплекте 2 аккумулятора. Фонарь работает как Power Bank — подзарядит телефон в дороге, заряд виден в процентах.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Что умеет&lt;/strong&gt;&lt;br&gt;▪️ Мощный дальний луч с фокусировкой&lt;br&gt;▪️ 4 режима фонаря: 100%, 50%, стробоскоп, SOS&lt;br&gt;▪️ Боковой кемпинг-свет: белый, красный, синий — до 48 часов работы&lt;br&gt;▪️ Прикуриватель — разжечь костёр, свечу, горелку&lt;br&gt;▪️ Корпус из авиационного алюминия, выдерживает мороз до –30 °C&lt;br&gt;▪️ Ударный торец — выбить стекло в экстренной ситуации&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Где пригодится&lt;/strong&gt;&lt;br&gt;🚗 На трассе ночью — и дорогу подсветит, и огонь даст&lt;br&gt;🏕 В походе и на рыбалке — свет для лагеря и розжиг костра&lt;br&gt;🏠 Дома — когда отключили электричество&lt;/p&gt;&lt;p&gt;🎁 Подарок мужчине, который оценит: автомобилисту, рыбаку, охотнику.&lt;/p&gt;&lt;p&gt;🛡 Гарантия 1 год. Новый, в подарочной коробке.&lt;br&gt;🚚 Авито Доставка по всей России, отправка в день заказа.&lt;br&gt;💸 Скидка 10% при заказе от 2 товаров — применится автоматически.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.RZyqOraw6XWcjWt4rFc7gfyb63Uak-F_HA.ZhkfV2jUodsDNjsJKBG1zY9N5FZFMba265I3qPewz10 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.1GUXyLaweIwhf_qBM_fxe0FpeoynYXCGoQ.jXcMkzeT3nPFcs_asfZ4xjU28cTXMVK5q50DTxHav0M | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.-UrHb7awVaPx2NeuuTDUV5HOV6N3xl2pcQ.13DADuLXGMPKzGLzO6f0fQxhkkOYRMbUnuB9hL5bQ2o | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.EsWNqrawviy7HTwhpbZx2tsLvCw9A7YmOw.LjhOVO0T--Dx7yt7Jyb6O48BW1yTAREmEqReu_tVec0 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.9dyrJbawWTWdkts4zWqUw_2EWzUbjFE_HQ.gKCJlMeRAz_SyboX88jNzktu3b-c_q9eQlSBhvSSrOs | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.qnZlkLawBp9TJ4SSPYqkT0gwBJ_VOQ6V0w.4YXoF0j_5i5MFvSQ-nVrfrNgvfl0kVdbf6vQTb95O6w | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.Xfcx9Law8R4HQ3MTB4k96mdV8x6BXfkUhw.NoIqtNereUIM3us3O4_2QuOlrOgPUqvuYQxE_AmfwSI | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.ibsqSbawJVIc_qdfNBvLggfpJ1Ka4C1YnA.1ohYUU4KFiKtE9Z12SzWM3x3nJUCk-WOgANvv8_gB5U | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.h6hxkbawK0FHJqlMc8OptScwKUHBOCNLxw.oHdgx3TTLWwI2TWSnzIF3Nft3H-GhatYF_VKTOZ4qp0</t>
+          <t xml:space="preserve">https://iili.io/nYjwLge.jpg | https://iili.io/nYjNpvs.jpg | https://iili.io/nYjO0AJ.jpg | https://iili.io/nYjOZDx.jpg | https://iili.io/nYjvVMQ.jpg | https://iili.io/nYj8qWx.jpg | https://iili.io/nYj8js4.jpg | https://iili.io/nYjS2rN.jpg | https://iili.io/nYjUK6Q.jpg | https://iili.io/nYjrWa2.jpg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -8641,11 +8621,6 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>2026-10-07T20:01:57+03:00</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
@@ -8654,11 +8629,6 @@
       <c r="U13" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Активно</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9306,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Самый Мощный Бинокль с Зумом "Титан"</t>
+          <t xml:space="preserve">Самый Мощный Бинокль 20х60 «Титан» BaK-4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/acc1_feed.xlsx
+++ b/acc1_feed.xlsx
@@ -3013,7 +3013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="50" customHeight="1">
@@ -3114,27 +3114,32 @@
           <t>Способ доставки</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало размещения</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>AvitoStatus</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>AvitoDateEnd</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="V2" s="7" t="inlineStr">
         <is>
           <t>Почта</t>
         </is>
       </c>
-      <c r="V2" s="7" t="inlineStr">
+      <c r="W2" s="7" t="inlineStr">
         <is>
           <t>Название компании</t>
         </is>
       </c>
-      <c r="W2" s="7" t="n"/>
+      <c r="X2" s="7" t="n"/>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -3228,6 +3233,11 @@
           <t>Необязательный</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -3310,6 +3320,11 @@
           <t>Одно значение из выпадающего списка в ячейке</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробнее о параметре</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3402,22 +3417,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2026-10-05T15:22:07+03:00</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -3514,22 +3529,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2026-10-10T19:54:31+03:00</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -3626,22 +3641,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>2026-10-21T13:48:55+03:00</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -3738,22 +3753,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>2026-10-22T10:26:51+03:00</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -3850,22 +3865,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>2026-09-25T16:59:33+03:00</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -3962,22 +3977,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>2026-10-20T11:27:53+03:00</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -4074,22 +4089,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>2026-10-15T15:39:26+03:00</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -4186,22 +4201,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>2026-10-10T12:39:32+03:00</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -4298,22 +4313,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>2026-10-19T20:04:31+03:00</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -4410,22 +4425,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>2026-09-28T15:05:08+03:00</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -4524,20 +4539,25 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t xml:space="preserve">2027-04-01</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>2026-09-30T17:41:02+03:00</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -4634,22 +4654,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>2026-10-21T15:00:41+03:00</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -4746,22 +4766,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>2026-10-21T12:22:46+03:00</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -4858,22 +4878,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>2026-10-08T12:03:26+03:00</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -4965,12 +4985,12 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -5067,22 +5087,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>2026-10-02T19:54:03+03:00</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -5179,22 +5199,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>2026-10-09T20:23:39+03:00</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -5291,22 +5311,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>2026-10-09T20:15:16+03:00</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -5403,22 +5423,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>2026-10-19T17:13:39+03:00</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -5515,22 +5535,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>2026-09-28T14:42:23+03:00</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -5627,22 +5647,22 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Активно</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>2026-10-23T18:22:48+03:00</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
@@ -5729,12 +5749,12 @@
           <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>golodnov1daniil@gmail.com</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>РуГаджет РОЗНИЦА и ОПТ</t>
         </is>
